--- a/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0003T0006Z000C1N26_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T4883_W0074F0003T0006Z000C1N26_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>34.02341326842879</v>
+        <v>5.528804656119679</v>
       </c>
       <c r="D2" t="n">
-        <v>24.30674716229589</v>
+        <v>3.949846413873082</v>
       </c>
       <c r="E2" t="n">
-        <v>7.393841698703016</v>
+        <v>1.20149927603924</v>
       </c>
       <c r="F2" t="n">
-        <v>2.046602368904251</v>
+        <v>0.3325728849469407</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>19.23572987102276</v>
+        <v>3.125806104041199</v>
       </c>
       <c r="D3" t="n">
-        <v>20.21354242448739</v>
+        <v>3.284700643979201</v>
       </c>
       <c r="E3" t="n">
-        <v>7.393841698703016</v>
+        <v>1.20149927603924</v>
       </c>
       <c r="F3" t="n">
-        <v>2.046602368904251</v>
+        <v>0.3325728849469407</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
